--- a/assets/constructions/examples/ctd_bs_carti_solid.xlsx
+++ b/assets/constructions/examples/ctd_bs_carti_solid.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,11 +554,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CA0807-37</t>
+          <t>CA0804-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -577,13 +602,13 @@
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="I2" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -623,7 +648,7 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,13 +656,24 @@
       <c r="Y2" t="inlineStr">
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CA0803-16</t>
+          <t>CA0808-42</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -656,13 +692,13 @@
         <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -702,7 +738,7 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -710,25 +746,32 @@
       <c r="Y3" t="inlineStr">
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IHAXF 2.5-4/8</t>
+          <t>CA0807-37</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ISCAR</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>IHAXF</t>
-        </is>
-      </c>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>PMK</t>
@@ -739,20 +782,16 @@
         <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>43</v>
-      </c>
-      <c r="K4" t="n">
-        <v>43</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -764,12 +803,10 @@
       <c r="N4" t="b">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DAN_HB-8</t>
+          <t>HB-8</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -782,7 +819,7 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -790,28 +827,45 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0.04</v>
+      </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020 / www.iscar.com</t>
+          <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CA0806-32</t>
+          <t>IHAXF 2.5-4/8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>ISCAR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>IHAXF</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>PMK</t>
@@ -822,16 +876,20 @@
         <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>32</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>12.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>43</v>
+      </c>
+      <c r="K5" t="n">
+        <v>43</v>
+      </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
@@ -843,10 +901,12 @@
       <c r="N5" t="b">
         <v>0</v>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>HB-8</t>
+          <t>DAN_HB-8</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -859,7 +919,7 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -867,22 +927,31 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="W5" t="n">
-        <v>0.04</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
+          <t>2020 / www.iscar.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CA0808-42</t>
+          <t>CA0805-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -901,13 +970,13 @@
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="I6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -947,7 +1016,7 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,6 +1024,17 @@
       <c r="Y6" t="inlineStr">
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
